--- a/SAEN PEÑA/Agosto/SAENZ_EXPENSAS-Agosto.xlsx
+++ b/SAEN PEÑA/Agosto/SAENZ_EXPENSAS-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2D2D6A-F993-4B77-BABE-FA864202D046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E3CB6F-83E0-4E47-8831-C5E544DC957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="prorrateo  (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t>UF</t>
   </si>
@@ -235,16 +235,19 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Liquidacion mes de JULIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Período JULIO </t>
-  </si>
-  <si>
     <t>Camion Villar -  Destapaciones 22/07</t>
   </si>
   <si>
     <t>PRESUPUESTO APROBADO - GASTO FLETE PROYECTADO</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de AGOSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período AGOSTO </t>
+  </si>
+  <si>
+    <t>Salvatierra Nicolas - Trabajos realizados para intentar desobstruir camara septica - No se consigue, se encuentra pozo lleno y se sugiere desagotar</t>
   </si>
 </sst>
 </file>
@@ -367,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +419,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1055,7 +1064,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1245,63 +1254,6 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1310,9 +1262,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1327,6 +1276,79 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1694,23 +1716,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1718,27 +1740,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1746,11 +1768,11 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
       <c r="E7" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" s="103"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1758,24 +1780,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="106" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="102"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="113"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="125"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="104"/>
       <c r="B12" s="104"/>
       <c r="C12" s="112"/>
@@ -1787,14 +1809,14 @@
         <v>368212.76895173313</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="102" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="111">
+      <c r="C13" s="112">
         <v>35601</v>
       </c>
       <c r="D13" s="36"/>
@@ -1806,26 +1828,26 @@
         <v>123127.97509600001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="104" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="111">
-        <v>34213.629999999997</v>
+      <c r="C14" s="112">
+        <v>33767.160000000003</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="51" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="52">
-        <f>-(C35)</f>
-        <v>-355359.13500000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <f>-(C37)</f>
+        <v>-1422492.925</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="102" t="s">
         <v>21</v>
       </c>
@@ -1838,22 +1860,22 @@
       <c r="E15" s="51"/>
       <c r="F15" s="52"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="107"/>
       <c r="B16" s="108"/>
       <c r="C16" s="82">
         <f>SUM(C12:C15)</f>
-        <v>102614.63</v>
+        <v>102168.16</v>
       </c>
       <c r="E16" s="53" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="54">
         <f>SUM(F12:F15)</f>
-        <v>135981.60904773313</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-931152.18095226691</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="106" t="s">
         <v>23</v>
       </c>
@@ -1863,12 +1885,12 @@
       <c r="E17" s="19"/>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="102" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" s="75">
         <f xml:space="preserve"> 51328.1+51328.1*5%</f>
@@ -1878,9 +1900,9 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="102" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B19" s="110"/>
       <c r="C19" s="75">
@@ -1890,213 +1912,236 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111">
-        <v>18850</v>
+    <row r="20" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="145" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="146"/>
+      <c r="C20" s="147">
+        <v>73600</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="102" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="110"/>
-      <c r="C21" s="111">
-        <v>200000</v>
+    <row r="21" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="148"/>
+      <c r="B21" s="149"/>
+      <c r="C21" s="147">
+        <v>993980.26</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="107"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="82">
-        <f>SUM(C17:C21)</f>
-        <v>452744.505</v>
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="110"/>
+      <c r="C22" s="111">
+        <v>18850</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42">
-        <f>+C22+C16</f>
-        <v>555359.13500000001</v>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="110"/>
+      <c r="C23" s="111">
+        <v>200000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="107"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="82">
+        <f>SUM(C17:C23)</f>
+        <v>1520324.7650000001</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42">
+        <f>+C24+C16</f>
+        <v>1622492.925</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="78"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="B26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="47"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="46">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="55"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="46">
-        <v>0</v>
-      </c>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="37"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="47"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="76"/>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="46">
+        <v>0</v>
+      </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="81"/>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="55"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="46">
+        <v>0</v>
+      </c>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="73"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="76">
-        <v>0</v>
-      </c>
+      <c r="B31" s="74"/>
+      <c r="C31" s="76"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="73"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="81"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="73"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="76">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59">
-        <f>SUM(C27:C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B34" s="58"/>
+      <c r="C34" s="59">
+        <f>SUM(C29:C33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="46">
-        <f>C23-C21</f>
-        <v>355359.13500000001</v>
-      </c>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="C35" s="46">
+        <f>C25-C23</f>
+        <v>1422492.925</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="72">
-        <f>+C23</f>
-        <v>555359.13500000001</v>
-      </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="57" t="s">
+      <c r="C36" s="72">
+        <f>+C25</f>
+        <v>1622492.925</v>
+      </c>
+      <c r="E36" s="105"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="59">
-        <f>C33</f>
-        <v>355359.13500000001</v>
-      </c>
-      <c r="E35" s="16"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="58"/>
+      <c r="C37" s="59">
+        <f>C35</f>
+        <v>1422492.925</v>
+      </c>
+      <c r="E37" s="16"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D44" s="16"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="19"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="20"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D46" s="16"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="19"/>
       <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="20"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2114,24 +2159,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="100" t="s">
         <v>60</v>
       </c>
@@ -2153,10 +2198,10 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="66" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de JULIO</v>
+        <v>Liquidacion mes de AGOSTO</v>
       </c>
       <c r="B2" s="67"/>
       <c r="C2" s="67"/>
@@ -2172,7 +2217,7 @@
       <c r="K2" s="70"/>
       <c r="L2" s="71"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2210,7 +2255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2240,7 +2285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2284,7 +2329,7 @@
         <v>83970.301212000006</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2325,7 +2370,7 @@
         <v>154602.20380062901</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2366,7 +2411,7 @@
         <v>190608.52024670265</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2407,7 +2452,7 @@
         <v>238561.86478411587</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2451,7 +2496,7 @@
         <v>88413.174292000011</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2492,7 +2537,7 @@
         <v>109003.0592478312</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2535,24 +2580,24 @@
         <v>865159.12358327874</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="114"/>
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="114"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="126"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="126"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2569,68 +2614,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134"/>
       <c r="F1" s="83"/>
       <c r="G1" s="83"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="123" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126">
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138">
         <v>565</v>
       </c>
-      <c r="E2" s="127"/>
+      <c r="E2" s="139"/>
       <c r="F2" s="84"/>
       <c r="G2" s="84"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="128" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="128" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="115" t="s">
+      <c r="E3" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="115" t="s">
+      <c r="F3" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="115" t="s">
+      <c r="G3" s="127" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="129"/>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="141"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85">
         <v>1</v>
       </c>
@@ -2653,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="85">
         <v>2</v>
       </c>
@@ -2676,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="85">
         <v>3</v>
       </c>
@@ -2699,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="85">
         <v>4</v>
       </c>
@@ -2722,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="85">
         <v>5</v>
       </c>
@@ -2745,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="90">
         <v>6</v>
       </c>
@@ -2768,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="95" t="s">
         <v>10</v>
       </c>
@@ -2787,12 +2832,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="117"/>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="129"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="83"/>
       <c r="G12" s="83"/>
     </row>
@@ -2821,36 +2866,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="132" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="136">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="144">
         <v>1200000</v>
       </c>
-      <c r="H1" s="136"/>
-      <c r="I1" s="137"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H1" s="144"/>
+      <c r="I1" s="117"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2879,7 +2924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2900,7 +2945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2910,7 +2955,7 @@
       <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="138">
+      <c r="D4" s="118">
         <v>0.1512</v>
       </c>
       <c r="E4" s="34">
@@ -2919,12 +2964,12 @@
       <c r="F4" s="75">
         <v>0</v>
       </c>
-      <c r="G4" s="139">
+      <c r="G4" s="119">
         <f>E4-F4</f>
         <v>0</v>
       </c>
       <c r="H4" s="34">
-        <f>G$1*D4</f>
+        <f t="shared" ref="H4:H9" si="0">G$1*D4</f>
         <v>181440</v>
       </c>
       <c r="I4" s="34">
@@ -2932,7 +2977,7 @@
         <v>181440</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2942,7 +2987,7 @@
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="138">
+      <c r="D5" s="118">
         <v>0.15690000000000001</v>
       </c>
       <c r="E5" s="34">
@@ -2951,20 +2996,20 @@
       <c r="F5" s="75">
         <v>0</v>
       </c>
-      <c r="G5" s="139">
-        <f t="shared" ref="G5:G7" si="0">E5-F5</f>
+      <c r="G5" s="119">
+        <f t="shared" ref="G5:G7" si="1">E5-F5</f>
         <v>0</v>
       </c>
       <c r="H5" s="34">
-        <f>G$1*D5</f>
+        <f t="shared" si="0"/>
         <v>188280</v>
       </c>
       <c r="I5" s="34">
-        <f t="shared" ref="I5:I9" si="1">H5</f>
+        <f t="shared" ref="I5:I9" si="2">H5</f>
         <v>188280</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2974,7 +3019,7 @@
       <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="138">
+      <c r="D6" s="118">
         <v>0.15820000000000001</v>
       </c>
       <c r="E6" s="34">
@@ -2983,20 +3028,20 @@
       <c r="F6" s="75">
         <v>0</v>
       </c>
-      <c r="G6" s="139">
+      <c r="G6" s="119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="34">
-        <f>G$1*D6</f>
         <v>189840</v>
       </c>
       <c r="I6" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>189840</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -3006,7 +3051,7 @@
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="138">
+      <c r="D7" s="118">
         <v>0.19800000000000001</v>
       </c>
       <c r="E7" s="34">
@@ -3015,20 +3060,20 @@
       <c r="F7" s="75">
         <v>0</v>
       </c>
-      <c r="G7" s="139">
+      <c r="G7" s="119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="34">
-        <f>G$1*D7</f>
         <v>237600</v>
       </c>
       <c r="I7" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>237600</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -3038,7 +3083,7 @@
       <c r="C8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="138">
+      <c r="D8" s="118">
         <v>0.15920000000000001</v>
       </c>
       <c r="E8" s="34">
@@ -3047,20 +3092,20 @@
       <c r="F8" s="75">
         <v>0</v>
       </c>
-      <c r="G8" s="139">
+      <c r="G8" s="119">
         <f>E8-F8</f>
         <v>0</v>
       </c>
       <c r="H8" s="34">
-        <f>G$1*D8</f>
+        <f t="shared" si="0"/>
         <v>191040</v>
       </c>
       <c r="I8" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>191040</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -3070,7 +3115,7 @@
       <c r="C9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="138">
+      <c r="D9" s="118">
         <v>0.17649999999999999</v>
       </c>
       <c r="E9" s="34">
@@ -3079,31 +3124,31 @@
       <c r="F9" s="75">
         <v>0</v>
       </c>
-      <c r="G9" s="139">
+      <c r="G9" s="119">
         <f>E9-F9</f>
         <v>0</v>
       </c>
       <c r="H9" s="34">
-        <f>G$1*D9</f>
+        <f t="shared" si="0"/>
         <v>211800</v>
       </c>
       <c r="I9" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211800</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="141"/>
-      <c r="C10" s="142"/>
-      <c r="D10" s="143">
+      <c r="B10" s="121"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="123">
         <f>SUM(D4:D9)</f>
         <v>1</v>
       </c>
       <c r="E10" s="43">
-        <f t="shared" ref="E10" si="2">SUM(E4:E9)</f>
+        <f t="shared" ref="E10" si="3">SUM(E4:E9)</f>
         <v>0</v>
       </c>
       <c r="F10" s="43">
@@ -3114,8 +3159,8 @@
         <f>SUM(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="144">
-        <f t="shared" ref="H10" si="3">SUM(H4:H9)</f>
+      <c r="H10" s="124">
+        <f t="shared" ref="H10" si="4">SUM(H4:H9)</f>
         <v>1200000</v>
       </c>
       <c r="I10" s="43">
@@ -3123,21 +3168,21 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="126"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>

--- a/SAEN PEÑA/Agosto/SAENZ_EXPENSAS-Agosto.xlsx
+++ b/SAEN PEÑA/Agosto/SAENZ_EXPENSAS-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E3CB6F-83E0-4E47-8831-C5E544DC957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495F02FA-2AE1-459D-9695-4FCE886C08E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="prorrateo  (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="75">
   <si>
     <t>UF</t>
   </si>
@@ -235,12 +235,6 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Camion Villar -  Destapaciones 22/07</t>
-  </si>
-  <si>
-    <t>PRESUPUESTO APROBADO - GASTO FLETE PROYECTADO</t>
-  </si>
-  <si>
     <t>Liquidacion mes de AGOSTO</t>
   </si>
   <si>
@@ -248,6 +242,15 @@
   </si>
   <si>
     <t>Salvatierra Nicolas - Trabajos realizados para intentar desobstruir camara septica - No se consigue, se encuentra pozo lleno y se sugiere desagotar</t>
+  </si>
+  <si>
+    <t>Materiales para la obra</t>
+  </si>
+  <si>
+    <t>Ingreso por pago de materiales de obra</t>
+  </si>
+  <si>
+    <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
 </sst>
 </file>
@@ -261,7 +264,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,8 +372,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,12 +429,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1064,7 +1068,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1129,7 +1133,6 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1276,9 +1279,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1335,19 +1346,6 @@
     </xf>
     <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1716,63 +1714,63 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="101" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
       <c r="E7" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="103"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="F7" s="102"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1780,363 +1778,357 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="106" t="s">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="102"/>
+      <c r="B11" s="101"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="125" t="s">
+      <c r="E11" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="125"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="104"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="112"/>
+      <c r="F11" s="126"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="103"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="111"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="50">
-        <v>368212.76895173313</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="102" t="s">
+      <c r="F12" s="49">
+        <v>135981.60904773313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="112">
+      <c r="C13" s="110">
         <v>35601</v>
       </c>
       <c r="D13" s="36"/>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="52">
+      <c r="F13" s="51">
         <f>'prorrateo '!F11</f>
-        <v>123127.97509600001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+        <v>781188.82237127877</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="112">
+      <c r="C14" s="110">
         <v>33767.160000000003</v>
       </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="52">
-        <f>-(C37)</f>
-        <v>-1422492.925</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="102" t="s">
+      <c r="F14" s="51">
+        <f>-(C36)</f>
+        <v>-232356.86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="74">
         <v>32800</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="107"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="82">
-        <f>SUM(C12:C15)</f>
+      <c r="D15" s="5"/>
+      <c r="E15" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="51">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="101"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="74"/>
+      <c r="E16" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="51">
+        <v>-993980.26</v>
+      </c>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="106"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="81">
+        <f>SUM(C12:C16)</f>
         <v>102168.16</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E17" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="54">
-        <f>SUM(F12:F15)</f>
-        <v>-931152.18095226691</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="106" t="s">
+      <c r="F17" s="53">
+        <f>SUM(F12:F16)</f>
+        <v>890833.31141901179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="110" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="75">
-        <f xml:space="preserve"> 51328.1+51328.1*5%</f>
-        <v>53894.504999999997</v>
-      </c>
+      <c r="B18" s="101"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="102" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="110"/>
-      <c r="C19" s="75">
-        <v>180000</v>
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="101" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="109" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="74">
+        <f xml:space="preserve"> 53894+53894*5%</f>
+        <v>56588.7</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="145" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="146"/>
-      <c r="C20" s="147">
+    <row r="20" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="127" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="128"/>
+      <c r="C20" s="74">
         <v>73600</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="148"/>
-      <c r="B21" s="149"/>
-      <c r="C21" s="147">
-        <v>993980.26</v>
-      </c>
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="109"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="110"/>
-      <c r="C22" s="111">
-        <v>18850</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="101" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="109"/>
+      <c r="C22" s="110">
+        <f>555359-232356.86</f>
+        <v>323002.14</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="102" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="111">
-        <v>200000</v>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="106"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="124">
+        <f>SUM(C18:C22)</f>
+        <v>453190.84</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="107"/>
-      <c r="B24" s="108"/>
-      <c r="C24" s="82">
-        <f>SUM(C17:C23)</f>
-        <v>1520324.7650000001</v>
+      <c r="E23" s="5"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="125">
+        <f>+C23+C17</f>
+        <v>555359</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="42">
-        <f>+C24+C16</f>
-        <v>1622492.925</v>
-      </c>
-      <c r="D25" s="5"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63" t="s">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="47"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="46"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="45">
+        <v>0</v>
+      </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="46">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="54"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="45">
         <v>0</v>
       </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="55"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="46">
-        <v>0</v>
-      </c>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="72"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="75"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="76"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="72"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="80"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="81"/>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="72"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="75">
+        <v>0</v>
+      </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="73"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="76">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="59">
-        <f>SUM(C29:C33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B33" s="57"/>
+      <c r="C33" s="58">
+        <f>SUM(C28:C32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="46">
-        <f>C25-C23</f>
-        <v>1422492.925</v>
-      </c>
+      <c r="C34" s="45">
+        <f>C24-C22</f>
+        <v>232356.86</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="71">
+        <f>+C24</f>
+        <v>555359</v>
+      </c>
+      <c r="E35" s="104"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="72">
-        <f>+C25</f>
-        <v>1622492.925</v>
-      </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="57" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="58"/>
-      <c r="C37" s="59">
-        <f>C35</f>
-        <v>1422492.925</v>
-      </c>
-      <c r="E37" s="16"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="57"/>
+      <c r="C36" s="58">
+        <f>C34</f>
+        <v>232356.86</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="16"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="19"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="20"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="18"/>
       <c r="B58" s="18"/>
-      <c r="C58" s="20"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="18"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2159,29 +2151,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
       <c r="D1" s="26"/>
       <c r="E1" s="25" t="s">
         <v>41</v>
@@ -2193,31 +2185,31 @@
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
-      <c r="K1" s="65">
+      <c r="K1" s="64">
         <v>555359.13500000001</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66" t="str">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de AGOSTO</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="69" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="71"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="70"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2255,7 +2247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2281,11 +2273,11 @@
       <c r="K4" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="60" t="s">
+      <c r="L4" s="59" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2299,19 +2291,16 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>59977.286838</v>
-      </c>
-      <c r="F5" s="75">
-        <f t="shared" ref="F5" si="0">E5</f>
-        <v>59977.286838</v>
-      </c>
-      <c r="G5" s="61">
+        <v>83970.301212000006</v>
+      </c>
+      <c r="F5" s="74"/>
+      <c r="G5" s="60">
         <f>E5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="64">
+        <v>83970.301212000006</v>
+      </c>
+      <c r="H5" s="63">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>0</v>
+        <v>7053.5053018080007</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2326,10 +2315,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>83970.301212000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>174994.10772580802</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2343,16 +2332,19 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>62238.335349750007</v>
-      </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="61">
+        <v>154602.20380062901</v>
+      </c>
+      <c r="F6" s="74">
+        <f t="shared" ref="F6:F10" si="0">E6</f>
+        <v>154602.20380062901</v>
+      </c>
+      <c r="G6" s="60">
         <f t="shared" ref="G6:G8" si="1">E6-F6</f>
-        <v>62238.335349750007</v>
-      </c>
-      <c r="H6" s="64">
+        <v>0</v>
+      </c>
+      <c r="H6" s="63">
         <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>5228.0201693790004</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2367,10 +2359,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>154602.20380062901</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>87135.848281500002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2384,16 +2376,19 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>94788.473329984001</v>
-      </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="61">
+        <v>190608.52024670265</v>
+      </c>
+      <c r="F7" s="74">
+        <f t="shared" si="0"/>
+        <v>190608.52024670265</v>
+      </c>
+      <c r="G7" s="60">
         <f t="shared" si="1"/>
-        <v>94788.473329984001</v>
-      </c>
-      <c r="H7" s="64">
+        <v>0</v>
+      </c>
+      <c r="H7" s="63">
         <f t="shared" si="2"/>
-        <v>7962.2317597186566</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2408,10 +2403,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>190608.52024670265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>87857.815157000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2425,16 +2420,19 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>118635.38381376001</v>
-      </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="61">
+        <v>238561.86478411587</v>
+      </c>
+      <c r="F8" s="74">
+        <f t="shared" si="0"/>
+        <v>238561.86478411587</v>
+      </c>
+      <c r="G8" s="60">
         <f t="shared" si="1"/>
-        <v>118635.38381376001</v>
-      </c>
-      <c r="H8" s="64">
+        <v>0</v>
+      </c>
+      <c r="H8" s="63">
         <f t="shared" si="2"/>
-        <v>9965.3722403558422</v>
+        <v>0</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -2449,10 +2447,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>238561.86478411587</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>109961.10873000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2466,17 +2464,17 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>63150.688258000002</v>
-      </c>
-      <c r="F9" s="75">
-        <f>E9</f>
-        <v>63150.688258000002</v>
-      </c>
-      <c r="G9" s="61">
+        <v>88413.174292000011</v>
+      </c>
+      <c r="F9" s="74">
+        <f t="shared" si="0"/>
+        <v>88413.174292000011</v>
+      </c>
+      <c r="G9" s="60">
         <f>E9-F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2496,7 +2494,7 @@
         <v>88413.174292000011</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2510,16 +2508,19 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>10131.154908054625</v>
-      </c>
-      <c r="F10" s="75"/>
-      <c r="G10" s="61">
+        <v>109003.0592478312</v>
+      </c>
+      <c r="F10" s="74">
+        <f t="shared" si="0"/>
+        <v>109003.0592478312</v>
+      </c>
+      <c r="G10" s="60">
         <f>E10-F10</f>
-        <v>10131.154908054625</v>
-      </c>
-      <c r="H10" s="64">
+        <v>0</v>
+      </c>
+      <c r="H10" s="63">
         <f t="shared" si="2"/>
-        <v>851.0170122765885</v>
+        <v>0</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
@@ -2534,10 +2535,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>109003.0592478312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>98020.887327499993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2549,19 +2550,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>408921.32249754865</v>
+        <v>865159.12358327874</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>123127.97509600001</v>
-      </c>
-      <c r="G11" s="43">
+        <v>781188.82237127877</v>
+      </c>
+      <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>285793.34740154864</v>
-      </c>
-      <c r="H11" s="43">
+        <v>83970.301212000006</v>
+      </c>
+      <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>24006.641181730087</v>
+        <v>7053.5053018080007</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2575,29 +2576,29 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>865159.12358327874</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="126"/>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>646382.94151380809</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="129"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2614,232 +2615,232 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="132" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="135" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="138">
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="141">
         <v>565</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="140" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="140" t="s">
+      <c r="E2" s="142"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="140" t="s">
+      <c r="C3" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="142" t="s">
+      <c r="D3" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="127" t="s">
+      <c r="E3" s="130" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="127" t="s">
+      <c r="F3" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="127" t="s">
+      <c r="G3" s="130" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="141"/>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="85">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="144"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="84">
         <v>1</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="85">
         <v>0.1512</v>
       </c>
-      <c r="E5" s="89">
+      <c r="E5" s="88">
         <v>85</v>
       </c>
-      <c r="F5" s="89">
-        <v>0</v>
-      </c>
-      <c r="G5" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="85">
+      <c r="F5" s="88">
+        <v>0</v>
+      </c>
+      <c r="G5" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="84">
         <v>2</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="85">
         <v>0.15690000000000001</v>
       </c>
-      <c r="E6" s="89">
+      <c r="E6" s="88">
         <v>89</v>
       </c>
-      <c r="F6" s="89">
-        <v>0</v>
-      </c>
-      <c r="G6" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="85">
+      <c r="F6" s="88">
+        <v>0</v>
+      </c>
+      <c r="G6" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="84">
         <v>3</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="85">
         <v>0.15820000000000001</v>
       </c>
-      <c r="E7" s="89">
+      <c r="E7" s="88">
         <v>89</v>
       </c>
-      <c r="F7" s="89">
-        <v>0</v>
-      </c>
-      <c r="G7" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="85">
+      <c r="F7" s="88">
+        <v>0</v>
+      </c>
+      <c r="G7" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="84">
         <v>4</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="85">
         <v>0.19800000000000001</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="88">
         <v>112</v>
       </c>
-      <c r="F8" s="89">
-        <v>0</v>
-      </c>
-      <c r="G8" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="85">
+      <c r="F8" s="88">
+        <v>0</v>
+      </c>
+      <c r="G8" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="84">
         <v>5</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>0.15920000000000001</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="88">
         <v>90</v>
       </c>
-      <c r="F9" s="89">
-        <v>0</v>
-      </c>
-      <c r="G9" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="90">
+      <c r="F9" s="88">
+        <v>0</v>
+      </c>
+      <c r="G9" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="89">
         <v>6</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="C10" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="90">
         <v>0.17649999999999999</v>
       </c>
-      <c r="E10" s="94">
+      <c r="E10" s="93">
         <v>100</v>
       </c>
-      <c r="F10" s="94">
-        <v>0</v>
-      </c>
-      <c r="G10" s="94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="95" t="s">
+      <c r="F10" s="93">
+        <v>0</v>
+      </c>
+      <c r="G10" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97">
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="96">
         <v>1</v>
       </c>
-      <c r="E11" s="97">
+      <c r="E11" s="96">
         <v>565</v>
       </c>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="98" t="s">
+      <c r="G11" s="97" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="129"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2866,36 +2867,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="144">
-        <v>1200000</v>
-      </c>
-      <c r="H1" s="144"/>
-      <c r="I1" s="117"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="112" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="147">
+        <v>4500000</v>
+      </c>
+      <c r="H1" s="147"/>
+      <c r="I1" s="116"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2924,7 +2925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2945,7 +2946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2955,29 +2956,29 @@
       <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="117">
         <v>0.1512</v>
       </c>
       <c r="E4" s="34">
         <v>0</v>
       </c>
-      <c r="F4" s="75">
-        <v>0</v>
-      </c>
-      <c r="G4" s="119">
+      <c r="F4" s="74">
+        <v>0</v>
+      </c>
+      <c r="G4" s="118">
         <f>E4-F4</f>
         <v>0</v>
       </c>
       <c r="H4" s="34">
         <f t="shared" ref="H4:H9" si="0">G$1*D4</f>
-        <v>181440</v>
+        <v>680400</v>
       </c>
       <c r="I4" s="34">
         <f>H4</f>
-        <v>181440</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>680400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2987,29 +2988,29 @@
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="118">
+      <c r="D5" s="117">
         <v>0.15690000000000001</v>
       </c>
       <c r="E5" s="34">
         <v>0</v>
       </c>
-      <c r="F5" s="75">
-        <v>0</v>
-      </c>
-      <c r="G5" s="119">
+      <c r="F5" s="74">
+        <v>0</v>
+      </c>
+      <c r="G5" s="118">
         <f t="shared" ref="G5:G7" si="1">E5-F5</f>
         <v>0</v>
       </c>
       <c r="H5" s="34">
         <f t="shared" si="0"/>
-        <v>188280</v>
+        <v>706050</v>
       </c>
       <c r="I5" s="34">
         <f t="shared" ref="I5:I9" si="2">H5</f>
-        <v>188280</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>706050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -3019,29 +3020,29 @@
       <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="118">
+      <c r="D6" s="117">
         <v>0.15820000000000001</v>
       </c>
       <c r="E6" s="34">
         <v>0</v>
       </c>
-      <c r="F6" s="75">
-        <v>0</v>
-      </c>
-      <c r="G6" s="119">
+      <c r="F6" s="74">
+        <v>0</v>
+      </c>
+      <c r="G6" s="118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H6" s="34">
         <f t="shared" si="0"/>
-        <v>189840</v>
+        <v>711900</v>
       </c>
       <c r="I6" s="34">
         <f t="shared" si="2"/>
-        <v>189840</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>711900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -3051,29 +3052,29 @@
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="118">
+      <c r="D7" s="117">
         <v>0.19800000000000001</v>
       </c>
       <c r="E7" s="34">
         <v>0</v>
       </c>
-      <c r="F7" s="75">
-        <v>0</v>
-      </c>
-      <c r="G7" s="119">
+      <c r="F7" s="74">
+        <v>0</v>
+      </c>
+      <c r="G7" s="118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="34">
         <f t="shared" si="0"/>
-        <v>237600</v>
+        <v>891000</v>
       </c>
       <c r="I7" s="34">
         <f t="shared" si="2"/>
-        <v>237600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>891000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -3083,29 +3084,29 @@
       <c r="C8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="118">
+      <c r="D8" s="117">
         <v>0.15920000000000001</v>
       </c>
       <c r="E8" s="34">
         <v>0</v>
       </c>
-      <c r="F8" s="75">
-        <v>0</v>
-      </c>
-      <c r="G8" s="119">
+      <c r="F8" s="74">
+        <v>0</v>
+      </c>
+      <c r="G8" s="118">
         <f>E8-F8</f>
         <v>0</v>
       </c>
       <c r="H8" s="34">
         <f t="shared" si="0"/>
-        <v>191040</v>
+        <v>716400</v>
       </c>
       <c r="I8" s="34">
         <f t="shared" si="2"/>
-        <v>191040</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>716400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -3115,74 +3116,74 @@
       <c r="C9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="118">
+      <c r="D9" s="117">
         <v>0.17649999999999999</v>
       </c>
       <c r="E9" s="34">
         <v>0</v>
       </c>
-      <c r="F9" s="75">
-        <v>0</v>
-      </c>
-      <c r="G9" s="119">
+      <c r="F9" s="74">
+        <v>0</v>
+      </c>
+      <c r="G9" s="118">
         <f>E9-F9</f>
         <v>0</v>
       </c>
       <c r="H9" s="34">
         <f t="shared" si="0"/>
-        <v>211800</v>
+        <v>794250</v>
       </c>
       <c r="I9" s="34">
         <f t="shared" si="2"/>
-        <v>211800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="120" t="s">
+        <v>794250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="123">
+      <c r="B10" s="120"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="122">
         <f>SUM(D4:D9)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="42">
         <f t="shared" ref="E10" si="3">SUM(E4:E9)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <f>SUM(F4:F9)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="42">
         <f>SUM(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="124">
+      <c r="H10" s="123">
         <f t="shared" ref="H10" si="4">SUM(H4:H9)</f>
-        <v>1200000</v>
-      </c>
-      <c r="I10" s="43">
+        <v>4500000</v>
+      </c>
+      <c r="I10" s="42">
         <f>SUM(I4:I9)</f>
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="126"/>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
